--- a/backend/CP_HEADERS_TEMPLATE.xlsx
+++ b/backend/CP_HEADERS_TEMPLATE.xlsx
@@ -9831,31 +9831,38 @@
           <t>5-6</t>
         </is>
       </c>
-      <c r="S19" s="44" t="inlineStr">
+      <c r="S19" s="5" t="inlineStr">
         <is>
           <t>7-8</t>
         </is>
       </c>
-      <c r="T19" s="44" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>9-10</t>
         </is>
       </c>
-      <c r="U19" s="44" t="inlineStr">
+      <c r="U19" s="5" t="inlineStr">
         <is>
           <t>11-12</t>
         </is>
       </c>
-      <c r="V19" s="44" t="inlineStr">
+      <c r="V19" s="5" t="inlineStr">
         <is>
           <t>13-14</t>
         </is>
       </c>
-      <c r="W19" s="44" t="inlineStr">
+      <c r="W19" s="5" t="inlineStr">
         <is>
           <t>15-16</t>
         </is>
       </c>
+      <c r="X19" s="5" t="n"/>
+      <c r="Y19" s="5" t="n"/>
+      <c r="Z19" s="5" t="n"/>
+      <c r="AA19" s="5" t="n"/>
+      <c r="AB19" s="5" t="n"/>
+      <c r="AC19" s="5" t="n"/>
+      <c r="AD19" s="5" t="n"/>
     </row>
     <row r="20" ht="16.5" customHeight="1">
       <c r="P20" s="37" t="inlineStr">
@@ -9873,16 +9880,26 @@
           <t>K 3-6</t>
         </is>
       </c>
-      <c r="S20" s="44" t="inlineStr">
+      <c r="S20" s="5" t="inlineStr">
         <is>
           <t>A 3-6</t>
         </is>
       </c>
-      <c r="T20" s="44" t="inlineStr">
+      <c r="T20" s="5" t="inlineStr">
         <is>
           <t>A 7-11</t>
         </is>
       </c>
+      <c r="U20" s="5" t="n"/>
+      <c r="V20" s="5" t="n"/>
+      <c r="W20" s="5" t="n"/>
+      <c r="X20" s="5" t="n"/>
+      <c r="Y20" s="5" t="n"/>
+      <c r="Z20" s="5" t="n"/>
+      <c r="AA20" s="5" t="n"/>
+      <c r="AB20" s="5" t="n"/>
+      <c r="AC20" s="5" t="n"/>
+      <c r="AD20" s="5" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1">
       <c r="P21" s="37" t="inlineStr">
@@ -9900,16 +9917,26 @@
           <t>6-12M</t>
         </is>
       </c>
-      <c r="S21" s="44" t="inlineStr">
+      <c r="S21" s="5" t="inlineStr">
         <is>
           <t>12-18M</t>
         </is>
       </c>
-      <c r="T21" s="44" t="inlineStr">
+      <c r="T21" s="5" t="inlineStr">
         <is>
           <t>18-24M</t>
         </is>
       </c>
+      <c r="U21" s="5" t="n"/>
+      <c r="V21" s="5" t="n"/>
+      <c r="W21" s="5" t="n"/>
+      <c r="X21" s="5" t="n"/>
+      <c r="Y21" s="5" t="n"/>
+      <c r="Z21" s="5" t="n"/>
+      <c r="AA21" s="5" t="n"/>
+      <c r="AB21" s="5" t="n"/>
+      <c r="AC21" s="5" t="n"/>
+      <c r="AD21" s="5" t="n"/>
     </row>
     <row r="22" ht="16.5" customHeight="1">
       <c r="P22" s="37" t="inlineStr">
@@ -9927,21 +9954,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="S22" s="44" t="inlineStr">
+      <c r="S22" s="5" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="T22" s="44" t="inlineStr">
+      <c r="T22" s="5" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="U22" s="44" t="inlineStr">
+      <c r="U22" s="5" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
+      <c r="V22" s="5" t="n"/>
+      <c r="W22" s="5" t="n"/>
+      <c r="X22" s="5" t="n"/>
+      <c r="Y22" s="5" t="n"/>
+      <c r="Z22" s="5" t="n"/>
+      <c r="AA22" s="5" t="n"/>
+      <c r="AB22" s="5" t="n"/>
+      <c r="AC22" s="5" t="n"/>
+      <c r="AD22" s="5" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1">
       <c r="A23" s="8" t="n">

--- a/backend/CP_HEADERS_TEMPLATE.xlsx
+++ b/backend/CP_HEADERS_TEMPLATE.xlsx
@@ -12,7 +12,7 @@
     <externalReference r:id="rId2"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$18:$BR$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$22:$BR$29</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -9668,21 +9668,21 @@
       <c r="BR17" s="63" t="n"/>
     </row>
     <row r="18" customFormat="1" s="34">
-      <c r="A18" s="65" t="n"/>
-      <c r="B18" s="65" t="n"/>
-      <c r="C18" s="65" t="n"/>
-      <c r="D18" s="65" t="n"/>
-      <c r="E18" s="65" t="n"/>
-      <c r="F18" s="65" t="n"/>
-      <c r="G18" s="65" t="n"/>
-      <c r="H18" s="65" t="n"/>
-      <c r="I18" s="65" t="n"/>
-      <c r="J18" s="65" t="n"/>
-      <c r="K18" s="65" t="n"/>
-      <c r="L18" s="65" t="n"/>
-      <c r="M18" s="65" t="n"/>
-      <c r="N18" s="65" t="n"/>
-      <c r="O18" s="65" t="n"/>
+      <c r="A18" s="63" t="n"/>
+      <c r="B18" s="63" t="n"/>
+      <c r="C18" s="63" t="n"/>
+      <c r="D18" s="63" t="n"/>
+      <c r="E18" s="63" t="n"/>
+      <c r="F18" s="63" t="n"/>
+      <c r="G18" s="63" t="n"/>
+      <c r="H18" s="63" t="n"/>
+      <c r="I18" s="63" t="n"/>
+      <c r="J18" s="63" t="n"/>
+      <c r="K18" s="63" t="n"/>
+      <c r="L18" s="63" t="n"/>
+      <c r="M18" s="63" t="n"/>
+      <c r="N18" s="63" t="n"/>
+      <c r="O18" s="63" t="n"/>
       <c r="P18" s="37" t="inlineStr">
         <is>
           <t>016- KIDS 1-14</t>
@@ -9758,64 +9758,79 @@
           <t>14</t>
         </is>
       </c>
-      <c r="AE18" s="65" t="n"/>
-      <c r="AF18" s="65" t="n"/>
-      <c r="AG18" s="65" t="n"/>
-      <c r="AH18" s="65" t="n"/>
-      <c r="AI18" s="65" t="n"/>
-      <c r="AJ18" s="65" t="n"/>
-      <c r="AK18" s="65" t="n"/>
-      <c r="AL18" s="65" t="n"/>
-      <c r="AM18" s="65" t="n"/>
+      <c r="AE18" s="63" t="n"/>
+      <c r="AF18" s="63" t="n"/>
+      <c r="AG18" s="63" t="n"/>
+      <c r="AH18" s="63" t="n"/>
+      <c r="AI18" s="63" t="n"/>
+      <c r="AJ18" s="63" t="n"/>
+      <c r="AK18" s="63" t="n"/>
+      <c r="AL18" s="63" t="n"/>
+      <c r="AM18" s="63" t="n"/>
       <c r="AN18" s="66" t="n"/>
-      <c r="AO18" s="65" t="n"/>
+      <c r="AO18" s="63" t="n"/>
       <c r="AP18" s="45" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="AQ18" s="65" t="n"/>
-      <c r="AR18" s="65" t="n"/>
+      <c r="AQ18" s="63" t="n"/>
+      <c r="AR18" s="63" t="n"/>
       <c r="AS18" s="45" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="AT18" s="65" t="n"/>
-      <c r="AU18" s="65" t="n"/>
+      <c r="AT18" s="63" t="n"/>
+      <c r="AU18" s="63" t="n"/>
       <c r="AV18" s="45" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="AW18" s="65" t="n"/>
-      <c r="AX18" s="65" t="n"/>
+      <c r="AW18" s="63" t="n"/>
+      <c r="AX18" s="63" t="n"/>
       <c r="AY18" s="45" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="AZ18" s="65" t="n"/>
-      <c r="BA18" s="65" t="n"/>
-      <c r="BB18" s="65" t="n"/>
-      <c r="BC18" s="65" t="n"/>
-      <c r="BD18" s="65" t="n"/>
+      <c r="AZ18" s="63" t="n"/>
+      <c r="BA18" s="63" t="n"/>
+      <c r="BB18" s="63" t="n"/>
+      <c r="BC18" s="63" t="n"/>
+      <c r="BD18" s="63" t="n"/>
       <c r="BE18" s="66" t="n"/>
-      <c r="BF18" s="66" t="n"/>
-      <c r="BG18" s="65" t="n"/>
+      <c r="BF18" s="64" t="n"/>
+      <c r="BG18" s="63" t="n"/>
       <c r="BH18" s="66" t="n"/>
       <c r="BI18" s="65" t="n"/>
-      <c r="BJ18" s="65" t="n"/>
-      <c r="BK18" s="65" t="n"/>
-      <c r="BL18" s="65" t="n"/>
-      <c r="BM18" s="65" t="n"/>
+      <c r="BJ18" s="63" t="n"/>
+      <c r="BK18" s="63" t="n"/>
+      <c r="BL18" s="63" t="n"/>
+      <c r="BM18" s="63" t="n"/>
       <c r="BN18" s="66" t="n"/>
       <c r="BO18" s="66" t="n"/>
-      <c r="BP18" s="65" t="n"/>
+      <c r="BP18" s="63" t="n"/>
       <c r="BQ18" s="66" t="n"/>
-      <c r="BR18" s="65" t="n"/>
+      <c r="BR18" s="63" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1">
+      <c r="A19" s="63" t="n"/>
+      <c r="B19" s="63" t="n"/>
+      <c r="C19" s="63" t="n"/>
+      <c r="D19" s="63" t="n"/>
+      <c r="E19" s="63" t="n"/>
+      <c r="F19" s="63" t="n"/>
+      <c r="G19" s="63" t="n"/>
+      <c r="H19" s="63" t="n"/>
+      <c r="I19" s="63" t="n"/>
+      <c r="J19" s="63" t="n"/>
+      <c r="K19" s="63" t="n"/>
+      <c r="L19" s="63" t="n"/>
+      <c r="M19" s="63" t="n"/>
+      <c r="N19" s="63" t="n"/>
+      <c r="O19" s="63" t="n"/>
       <c r="P19" s="37" t="inlineStr">
         <is>
           <t>017- KIDS ALT 3</t>
@@ -9863,8 +9878,52 @@
       <c r="AB19" s="5" t="n"/>
       <c r="AC19" s="5" t="n"/>
       <c r="AD19" s="5" t="n"/>
+      <c r="AE19" s="63" t="n"/>
+      <c r="AF19" s="63" t="n"/>
+      <c r="AG19" s="63" t="n"/>
+      <c r="AH19" s="63" t="n"/>
+      <c r="AI19" s="63" t="n"/>
+      <c r="AJ19" s="63" t="n"/>
+      <c r="AK19" s="63" t="n"/>
+      <c r="AL19" s="63" t="n"/>
+      <c r="AM19" s="63" t="n"/>
+      <c r="AO19" s="63" t="n"/>
+      <c r="AQ19" s="63" t="n"/>
+      <c r="AR19" s="63" t="n"/>
+      <c r="AT19" s="63" t="n"/>
+      <c r="AU19" s="63" t="n"/>
+      <c r="AW19" s="63" t="n"/>
+      <c r="AX19" s="63" t="n"/>
+      <c r="AZ19" s="63" t="n"/>
+      <c r="BA19" s="63" t="n"/>
+      <c r="BB19" s="63" t="n"/>
+      <c r="BC19" s="63" t="n"/>
+      <c r="BD19" s="63" t="n"/>
+      <c r="BF19" s="64" t="n"/>
+      <c r="BG19" s="63" t="n"/>
+      <c r="BJ19" s="63" t="n"/>
+      <c r="BK19" s="63" t="n"/>
+      <c r="BL19" s="63" t="n"/>
+      <c r="BM19" s="63" t="n"/>
+      <c r="BP19" s="63" t="n"/>
+      <c r="BR19" s="63" t="n"/>
     </row>
     <row r="20" ht="16.5" customHeight="1">
+      <c r="A20" s="63" t="n"/>
+      <c r="B20" s="63" t="n"/>
+      <c r="C20" s="63" t="n"/>
+      <c r="D20" s="63" t="n"/>
+      <c r="E20" s="63" t="n"/>
+      <c r="F20" s="63" t="n"/>
+      <c r="G20" s="63" t="n"/>
+      <c r="H20" s="63" t="n"/>
+      <c r="I20" s="63" t="n"/>
+      <c r="J20" s="63" t="n"/>
+      <c r="K20" s="63" t="n"/>
+      <c r="L20" s="63" t="n"/>
+      <c r="M20" s="63" t="n"/>
+      <c r="N20" s="63" t="n"/>
+      <c r="O20" s="63" t="n"/>
       <c r="P20" s="37" t="inlineStr">
         <is>
           <t>018 - SOCKS</t>
@@ -9900,8 +9959,52 @@
       <c r="AB20" s="5" t="n"/>
       <c r="AC20" s="5" t="n"/>
       <c r="AD20" s="5" t="n"/>
+      <c r="AE20" s="63" t="n"/>
+      <c r="AF20" s="63" t="n"/>
+      <c r="AG20" s="63" t="n"/>
+      <c r="AH20" s="63" t="n"/>
+      <c r="AI20" s="63" t="n"/>
+      <c r="AJ20" s="63" t="n"/>
+      <c r="AK20" s="63" t="n"/>
+      <c r="AL20" s="63" t="n"/>
+      <c r="AM20" s="63" t="n"/>
+      <c r="AO20" s="63" t="n"/>
+      <c r="AQ20" s="63" t="n"/>
+      <c r="AR20" s="63" t="n"/>
+      <c r="AT20" s="63" t="n"/>
+      <c r="AU20" s="63" t="n"/>
+      <c r="AW20" s="63" t="n"/>
+      <c r="AX20" s="63" t="n"/>
+      <c r="AZ20" s="63" t="n"/>
+      <c r="BA20" s="63" t="n"/>
+      <c r="BB20" s="63" t="n"/>
+      <c r="BC20" s="63" t="n"/>
+      <c r="BD20" s="63" t="n"/>
+      <c r="BF20" s="64" t="n"/>
+      <c r="BG20" s="63" t="n"/>
+      <c r="BJ20" s="63" t="n"/>
+      <c r="BK20" s="63" t="n"/>
+      <c r="BL20" s="63" t="n"/>
+      <c r="BM20" s="63" t="n"/>
+      <c r="BP20" s="63" t="n"/>
+      <c r="BR20" s="63" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1">
+      <c r="A21" s="63" t="n"/>
+      <c r="B21" s="63" t="n"/>
+      <c r="C21" s="63" t="n"/>
+      <c r="D21" s="63" t="n"/>
+      <c r="E21" s="63" t="n"/>
+      <c r="F21" s="63" t="n"/>
+      <c r="G21" s="63" t="n"/>
+      <c r="H21" s="63" t="n"/>
+      <c r="I21" s="63" t="n"/>
+      <c r="J21" s="63" t="n"/>
+      <c r="K21" s="63" t="n"/>
+      <c r="L21" s="63" t="n"/>
+      <c r="M21" s="63" t="n"/>
+      <c r="N21" s="63" t="n"/>
+      <c r="O21" s="63" t="n"/>
       <c r="P21" s="37" t="inlineStr">
         <is>
           <t>019 - BABY SWIM</t>
@@ -9937,8 +10040,52 @@
       <c r="AB21" s="5" t="n"/>
       <c r="AC21" s="5" t="n"/>
       <c r="AD21" s="5" t="n"/>
+      <c r="AE21" s="63" t="n"/>
+      <c r="AF21" s="63" t="n"/>
+      <c r="AG21" s="63" t="n"/>
+      <c r="AH21" s="63" t="n"/>
+      <c r="AI21" s="63" t="n"/>
+      <c r="AJ21" s="63" t="n"/>
+      <c r="AK21" s="63" t="n"/>
+      <c r="AL21" s="63" t="n"/>
+      <c r="AM21" s="63" t="n"/>
+      <c r="AO21" s="63" t="n"/>
+      <c r="AQ21" s="63" t="n"/>
+      <c r="AR21" s="63" t="n"/>
+      <c r="AT21" s="63" t="n"/>
+      <c r="AU21" s="63" t="n"/>
+      <c r="AW21" s="63" t="n"/>
+      <c r="AX21" s="63" t="n"/>
+      <c r="AZ21" s="63" t="n"/>
+      <c r="BA21" s="63" t="n"/>
+      <c r="BB21" s="63" t="n"/>
+      <c r="BC21" s="63" t="n"/>
+      <c r="BD21" s="63" t="n"/>
+      <c r="BF21" s="64" t="n"/>
+      <c r="BG21" s="63" t="n"/>
+      <c r="BJ21" s="63" t="n"/>
+      <c r="BK21" s="63" t="n"/>
+      <c r="BL21" s="63" t="n"/>
+      <c r="BM21" s="63" t="n"/>
+      <c r="BP21" s="63" t="n"/>
+      <c r="BR21" s="63" t="n"/>
     </row>
     <row r="22" ht="16.5" customHeight="1">
+      <c r="A22" s="65" t="n"/>
+      <c r="B22" s="65" t="n"/>
+      <c r="C22" s="65" t="n"/>
+      <c r="D22" s="65" t="n"/>
+      <c r="E22" s="65" t="n"/>
+      <c r="F22" s="65" t="n"/>
+      <c r="G22" s="65" t="n"/>
+      <c r="H22" s="65" t="n"/>
+      <c r="I22" s="65" t="n"/>
+      <c r="J22" s="65" t="n"/>
+      <c r="K22" s="65" t="n"/>
+      <c r="L22" s="65" t="n"/>
+      <c r="M22" s="65" t="n"/>
+      <c r="N22" s="65" t="n"/>
+      <c r="O22" s="65" t="n"/>
       <c r="P22" s="37" t="inlineStr">
         <is>
           <t>020 - MENS DENIM</t>
@@ -9978,6 +10125,35 @@
       <c r="AB22" s="5" t="n"/>
       <c r="AC22" s="5" t="n"/>
       <c r="AD22" s="5" t="n"/>
+      <c r="AE22" s="65" t="n"/>
+      <c r="AF22" s="65" t="n"/>
+      <c r="AG22" s="65" t="n"/>
+      <c r="AH22" s="65" t="n"/>
+      <c r="AI22" s="65" t="n"/>
+      <c r="AJ22" s="65" t="n"/>
+      <c r="AK22" s="65" t="n"/>
+      <c r="AL22" s="65" t="n"/>
+      <c r="AM22" s="65" t="n"/>
+      <c r="AO22" s="65" t="n"/>
+      <c r="AQ22" s="65" t="n"/>
+      <c r="AR22" s="65" t="n"/>
+      <c r="AT22" s="65" t="n"/>
+      <c r="AU22" s="65" t="n"/>
+      <c r="AW22" s="65" t="n"/>
+      <c r="AX22" s="65" t="n"/>
+      <c r="AZ22" s="65" t="n"/>
+      <c r="BA22" s="65" t="n"/>
+      <c r="BB22" s="65" t="n"/>
+      <c r="BC22" s="65" t="n"/>
+      <c r="BD22" s="65" t="n"/>
+      <c r="BF22" s="66" t="n"/>
+      <c r="BG22" s="65" t="n"/>
+      <c r="BJ22" s="65" t="n"/>
+      <c r="BK22" s="65" t="n"/>
+      <c r="BL22" s="65" t="n"/>
+      <c r="BM22" s="65" t="n"/>
+      <c r="BP22" s="65" t="n"/>
+      <c r="BR22" s="65" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1">
       <c r="A23" s="8" t="n">
@@ -13788,73 +13964,73 @@
       <c r="BR58" s="7" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A18:BR29"/>
+  <autoFilter ref="A22:BR29"/>
   <mergeCells count="65">
-    <mergeCell ref="BI2:BI14"/>
     <mergeCell ref="BQ15:BQ16"/>
-    <mergeCell ref="BO15:BO18"/>
-    <mergeCell ref="J2:J18"/>
-    <mergeCell ref="AM2:AM18"/>
+    <mergeCell ref="J2:J22"/>
+    <mergeCell ref="L2:L22"/>
+    <mergeCell ref="AJ2:AJ22"/>
+    <mergeCell ref="AL2:AL22"/>
+    <mergeCell ref="BE2:BE14"/>
+    <mergeCell ref="AX2:AX22"/>
+    <mergeCell ref="BP2:BP22"/>
+    <mergeCell ref="Q1:AD1"/>
+    <mergeCell ref="BQ17:BQ18"/>
+    <mergeCell ref="C2:C22"/>
+    <mergeCell ref="E2:E22"/>
+    <mergeCell ref="O2:O22"/>
+    <mergeCell ref="AN15:AN18"/>
+    <mergeCell ref="AI2:AI22"/>
+    <mergeCell ref="AK2:AK22"/>
+    <mergeCell ref="AM2:AM22"/>
+    <mergeCell ref="AO2:AO22"/>
+    <mergeCell ref="BH2:BH14"/>
+    <mergeCell ref="BA2:BA22"/>
+    <mergeCell ref="BC2:BC22"/>
+    <mergeCell ref="B2:B22"/>
+    <mergeCell ref="D2:D22"/>
+    <mergeCell ref="BI15:BI18"/>
+    <mergeCell ref="BD2:BD22"/>
+    <mergeCell ref="F2:F22"/>
+    <mergeCell ref="H2:H22"/>
+    <mergeCell ref="BQ2:BQ14"/>
+    <mergeCell ref="BJ2:BJ22"/>
+    <mergeCell ref="AF2:AF22"/>
+    <mergeCell ref="AH2:AH22"/>
+    <mergeCell ref="AR2:AR22"/>
+    <mergeCell ref="AT2:AT22"/>
     <mergeCell ref="AY2:AY13"/>
-    <mergeCell ref="BF2:BF18"/>
-    <mergeCell ref="AO2:AO18"/>
-    <mergeCell ref="AU2:AU18"/>
-    <mergeCell ref="AW2:AW18"/>
-    <mergeCell ref="BR2:BR18"/>
-    <mergeCell ref="BA2:BA18"/>
-    <mergeCell ref="I2:I18"/>
-    <mergeCell ref="BC2:BC18"/>
-    <mergeCell ref="AL2:AL18"/>
-    <mergeCell ref="BO2:BO14"/>
-    <mergeCell ref="B2:B18"/>
-    <mergeCell ref="BH2:BH14"/>
-    <mergeCell ref="D2:D18"/>
-    <mergeCell ref="AG2:AG18"/>
+    <mergeCell ref="AU2:AU22"/>
+    <mergeCell ref="AW2:AW22"/>
+    <mergeCell ref="G2:G22"/>
     <mergeCell ref="BN15:BN18"/>
-    <mergeCell ref="AJ2:AJ18"/>
-    <mergeCell ref="M2:M18"/>
-    <mergeCell ref="BL2:BL18"/>
-    <mergeCell ref="AE2:AE18"/>
-    <mergeCell ref="BM2:BM18"/>
-    <mergeCell ref="AX2:AX18"/>
-    <mergeCell ref="BD2:BD18"/>
-    <mergeCell ref="AP2:AP12"/>
-    <mergeCell ref="BE2:BE14"/>
+    <mergeCell ref="M2:M22"/>
     <mergeCell ref="AN2:AN14"/>
-    <mergeCell ref="K2:K18"/>
-    <mergeCell ref="BI15:BI18"/>
-    <mergeCell ref="BP2:BP18"/>
-    <mergeCell ref="F2:F18"/>
-    <mergeCell ref="AN15:AN18"/>
-    <mergeCell ref="H2:H18"/>
-    <mergeCell ref="N2:N18"/>
-    <mergeCell ref="AQ2:AQ18"/>
-    <mergeCell ref="Q1:AD1"/>
-    <mergeCell ref="A2:A18"/>
-    <mergeCell ref="BJ2:BJ18"/>
-    <mergeCell ref="BQ17:BQ18"/>
-    <mergeCell ref="C2:C18"/>
+    <mergeCell ref="AE2:AE22"/>
+    <mergeCell ref="BM2:BM22"/>
+    <mergeCell ref="AG2:AG22"/>
     <mergeCell ref="AV2:AV13"/>
-    <mergeCell ref="E2:E18"/>
-    <mergeCell ref="BQ2:BQ14"/>
-    <mergeCell ref="BG2:BG18"/>
-    <mergeCell ref="BH15:BH18"/>
+    <mergeCell ref="N2:N22"/>
     <mergeCell ref="AS2:AS13"/>
     <mergeCell ref="BE15:BE18"/>
+    <mergeCell ref="BI2:BI14"/>
+    <mergeCell ref="AZ2:AZ22"/>
+    <mergeCell ref="BB2:BB22"/>
+    <mergeCell ref="BO15:BO18"/>
+    <mergeCell ref="BL2:BL22"/>
+    <mergeCell ref="BO2:BO14"/>
+    <mergeCell ref="BF2:BF22"/>
+    <mergeCell ref="BR2:BR22"/>
+    <mergeCell ref="I2:I22"/>
+    <mergeCell ref="AP2:AP12"/>
+    <mergeCell ref="AQ2:AQ22"/>
+    <mergeCell ref="K2:K22"/>
+    <mergeCell ref="A2:A22"/>
+    <mergeCell ref="BH15:BH18"/>
     <mergeCell ref="BN2:BN14"/>
-    <mergeCell ref="AK2:AK18"/>
+    <mergeCell ref="BG2:BG22"/>
     <mergeCell ref="Q2:AD2"/>
-    <mergeCell ref="O2:O18"/>
-    <mergeCell ref="AF2:AF18"/>
-    <mergeCell ref="AR2:AR18"/>
-    <mergeCell ref="AH2:AH18"/>
-    <mergeCell ref="BK2:BK18"/>
-    <mergeCell ref="AT2:AT18"/>
-    <mergeCell ref="AI2:AI18"/>
-    <mergeCell ref="AZ2:AZ18"/>
-    <mergeCell ref="BB2:BB18"/>
-    <mergeCell ref="L2:L18"/>
-    <mergeCell ref="G2:G18"/>
+    <mergeCell ref="BK2:BK22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9"/>
